--- a/Result/profitability/6720.xlsx
+++ b/Result/profitability/6720.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM26"/>
+  <dimension ref="A1:AM27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3732,6 +3732,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6720</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>104</v>
+      </c>
+      <c r="D27" t="n">
+        <v>56</v>
+      </c>
+      <c r="E27" t="n">
+        <v>48</v>
+      </c>
+      <c r="F27" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="G27" t="n">
+        <v>14</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>13.11%</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>28</v>
+      </c>
+      <c r="J27" t="n">
+        <v>42</v>
+      </c>
+      <c r="K27" t="n">
+        <v>34</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.1475</v>
+      </c>
+      <c r="N27" t="n">
+        <v>53.83374999999999</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.6199999999999999</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.215686274509804</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>6.350000000000001</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.1595477386934674</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>3.708333333333333</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-9.410000000000004</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-0.1693664506839453</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK27" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
